--- a/Filtered_V3.0/COCNW_HCA_Florida_Northwest_Hospital.xlsx
+++ b/Filtered_V3.0/COCNW_HCA_Florida_Northwest_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -1875,7 +1890,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1920,22 +1935,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Candescent Health/Envision Healthcare (Candescent Health)-</t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2372,7 +2372,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2394,7 +2409,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2439,7 +2454,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2476,7 +2491,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-radord</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2522,21 +2537,6 @@
       <c r="P27" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3164,7 +3164,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3186,7 +3201,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3231,22 +3246,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3703,22 +3703,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Admissions </t>
+          <t>GE (CPN - Gold Standard)-ADMO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Clinical Monitoring Results </t>
+          <t>GE (CPN - Gold Standard)-ITSHMRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCSCMI</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Monitoring Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-ITS HM Results </t>
+          <t>GE (CPN - Gold Standard)-LABRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Lab Results (Discrete) </t>
+          <t>GE (CPN - Gold Standard)-PCSCMI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>PCSCMI</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">Clinical Monitoring Results </t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4608,6 +4608,21 @@
       <c r="P55" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4629,7 +4644,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4679,17 +4694,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4711,7 +4726,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4756,22 +4771,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4793,7 +4808,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4875,7 +4890,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4920,22 +4935,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5501,22 +5501,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5958,17 +5958,17 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6035,22 +6035,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6117,22 +6117,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6535,6 +6535,21 @@
       <c r="P81" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6556,7 +6571,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6606,17 +6621,17 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6653,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6688,17 +6703,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6735,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6770,7 +6785,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -6780,7 +6795,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6802,7 +6817,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6852,7 +6867,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -6862,7 +6877,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6884,7 +6899,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6934,17 +6949,17 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -6966,7 +6981,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7048,7 +7063,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7130,7 +7145,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7180,17 +7195,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7227,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7262,17 +7277,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7309,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7344,17 +7359,17 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7391,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7422,21 +7437,6 @@
       <c r="P92" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7566,6 +7566,21 @@
       <c r="P94" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7587,7 +7602,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7633,6 +7648,21 @@
       <c r="P95" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7684,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7704,17 +7734,17 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7736,7 +7766,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7786,17 +7816,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7848,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7900,7 +7930,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7950,7 +7980,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -7960,7 +7990,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7982,7 +8012,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8032,7 +8062,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8042,7 +8072,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -8064,7 +8094,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8146,7 +8176,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8196,17 +8226,17 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -8228,7 +8258,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8278,17 +8308,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8340,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8392,7 +8422,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8442,17 +8472,17 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8504,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8556,7 +8586,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8606,17 +8636,17 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8668,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8688,17 +8718,17 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8750,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8770,17 +8800,17 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8832,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8852,17 +8882,17 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8914,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8934,17 +8964,17 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8996,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9012,21 +9042,6 @@
       <c r="P112" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9063,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9094,21 +9109,6 @@
       <c r="P113" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9654,7 +9654,22 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9676,7 +9691,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9743,7 +9758,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9788,22 +9803,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9933,6 +9933,21 @@
       <c r="P125" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9954,7 +9969,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10004,17 +10019,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10036,7 +10051,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10086,17 +10101,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10133,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10168,7 +10183,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -10178,7 +10193,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10200,7 +10215,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10250,7 +10265,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10260,7 +10275,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -10282,7 +10297,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10332,7 +10347,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10342,7 +10357,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10364,7 +10379,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10414,17 +10429,17 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10461,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10496,17 +10511,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -10528,7 +10543,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10578,17 +10593,17 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10610,7 +10625,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10660,7 +10675,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -10670,7 +10685,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10707,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10742,17 +10757,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10789,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10820,21 +10835,6 @@
       <c r="P136" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>CWSO</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>SIU</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11319,6 +11319,21 @@
       <c r="P143" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -11340,7 +11355,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11390,17 +11405,17 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11437,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11472,17 +11487,17 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -11504,7 +11519,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11554,17 +11569,17 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11601,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11668,7 +11683,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11718,7 +11733,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -11728,7 +11743,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -11750,7 +11765,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11800,17 +11815,17 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -11832,7 +11847,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11882,17 +11897,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -11914,7 +11929,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11964,17 +11979,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -11996,7 +12011,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -12051,12 +12066,12 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12093,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12128,17 +12143,17 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12160,7 +12175,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12242,7 +12257,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12292,17 +12307,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12339,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12374,17 +12389,17 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12421,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12456,17 +12471,17 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12503,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12538,17 +12553,17 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12585,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12616,21 +12631,6 @@
       <c r="P159" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15559,6 +15559,21 @@
       <c r="P198" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -15580,7 +15595,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15630,17 +15645,17 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -15662,7 +15677,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15712,7 +15727,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -15722,7 +15737,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -15744,7 +15759,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15794,7 +15809,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -15804,7 +15819,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -15826,7 +15841,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15876,7 +15891,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -15886,7 +15901,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -15908,7 +15923,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15990,7 +16005,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -16040,17 +16055,17 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -16072,7 +16087,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16118,21 +16133,6 @@
       <c r="P205" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16776,6 +16776,21 @@
       <c r="P214" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16797,7 +16812,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16847,17 +16862,17 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16879,7 +16894,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16929,7 +16944,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -16939,7 +16954,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16961,7 +16976,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -17011,7 +17026,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -17021,7 +17036,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -17043,7 +17058,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17093,7 +17108,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -17103,7 +17118,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -17125,7 +17140,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17207,7 +17222,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -17257,17 +17272,17 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17289,7 +17304,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17335,21 +17350,6 @@
       <c r="P221" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-ITS HM Results </t>
+          <t>Mednax (BabySteps Cloud)-ITSHMRO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Admissions </t>
+          <t>Net Health (ReDoc Xfit)-ADMO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Charges </t>
+          <t>Net Health (ReDoc Xfit)-ITSHMRO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18961,17 +18961,17 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-ITS HM Results </t>
+          <t>Net Health (ReDoc Xfit)-OMORDO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19038,22 +19038,22 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-OM Orders </t>
+          <t>Net Health (ReDoc Xfit)-Patient Accounting</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19120,22 +19120,22 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19764,6 +19764,21 @@
       <c r="P253" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19785,7 +19800,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19831,21 +19846,6 @@
       <c r="P254" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rauland (Responder)-Admissions </t>
+          <t>Rauland (Responder)-ADMO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team Health (Team Health)-Admissions </t>
+          <t>Team Health (Team Health)-ADMO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20217,7 +20217,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20607,7 +20607,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telexy Healthcare Inc (Q-path)-Admissions </t>
+          <t>Telexy Healthcare Inc (Q-path)-ADMO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21270,7 +21270,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21835,6 +21835,21 @@
       <c r="P281" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -21856,7 +21871,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -21906,17 +21921,17 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -21938,7 +21953,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22020,7 +22035,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22102,7 +22117,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22184,7 +22199,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22234,17 +22249,17 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -22266,7 +22281,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22316,17 +22331,17 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -22348,7 +22363,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22398,17 +22413,17 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -22430,7 +22445,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22480,17 +22495,17 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22512,7 +22527,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22558,21 +22573,6 @@
       <c r="P290" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R290" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
